--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to fill this in" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -734,13 +734,3821 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2027-02-20</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2027-03-20</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2027-03-27</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2027-04-16</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2027-04-16</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2027-04-17</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2027-04-23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2027-04-23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2027-04-23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2027-05-07</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2027-05-07</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Munster</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ospreys</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Benetton</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Connacht</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Scarlets</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Dragons</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Stormers</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Zebre</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Leinster</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J145"/>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
+    <dataValidation sqref="C2:C145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
       <formula1>'Clubs'!$A$2:$A$17</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
+    <dataValidation sqref="D2:D145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
       <formula1>'Clubs'!$A$2:$A$17</formula1>
     </dataValidation>
   </dataValidations>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -532,7 +532,11 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
@@ -560,7 +564,11 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -588,7 +596,11 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-11.5</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -616,7 +628,11 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
@@ -644,7 +660,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -672,7 +692,11 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
@@ -700,7 +724,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
@@ -728,7 +756,11 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to fill this in" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$J$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$M$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -452,10 +452,13 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,22 +494,37 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>line_source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>home_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>away_score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>home_turnovers_conceded</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>away_turnovers_conceded</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>home_turnovers_won</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>away_turnovers_won</t>
         </is>
       </c>
     </row>
@@ -537,10 +555,13 @@
           <t>-9.5</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,10 +590,13 @@
           <t>-1.5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,10 +625,13 @@
           <t>-11.5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -633,10 +660,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,10 +695,13 @@
           <t>-2.5</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -697,10 +730,13 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -729,10 +765,13 @@
           <t>-12.5</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,10 +800,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -789,10 +831,13 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -817,10 +862,13 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -845,10 +893,13 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -873,10 +924,13 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -901,10 +955,13 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -929,10 +986,13 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -957,10 +1017,13 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -985,10 +1048,13 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1013,10 +1079,13 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1041,10 +1110,13 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1069,10 +1141,13 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1097,10 +1172,13 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1125,10 +1203,13 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1153,10 +1234,13 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1181,10 +1265,13 @@
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1209,10 +1296,13 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1237,10 +1327,13 @@
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1265,10 +1358,13 @@
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1293,10 +1389,13 @@
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1321,10 +1420,13 @@
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1349,10 +1451,13 @@
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1377,10 +1482,13 @@
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1405,10 +1513,13 @@
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1433,10 +1544,13 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1461,10 +1575,13 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1489,10 +1606,13 @@
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1517,10 +1637,13 @@
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1545,10 +1668,13 @@
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1573,10 +1699,13 @@
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1601,10 +1730,13 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1629,10 +1761,13 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1657,10 +1792,13 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1685,10 +1823,13 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1713,10 +1854,13 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1741,10 +1885,13 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1769,10 +1916,13 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1797,10 +1947,13 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1825,10 +1978,13 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1853,10 +2009,13 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1881,10 +2040,13 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1909,10 +2071,13 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1937,10 +2102,13 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1965,10 +2133,13 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1993,10 +2164,13 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2021,10 +2195,13 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2049,10 +2226,13 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2077,10 +2257,13 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2105,10 +2288,13 @@
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,10 +2319,13 @@
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2161,10 +2350,13 @@
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2189,10 +2381,13 @@
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2217,10 +2412,13 @@
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2245,10 +2443,13 @@
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2273,10 +2474,13 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2301,10 +2505,13 @@
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2329,10 +2536,13 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2357,10 +2567,13 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2385,10 +2598,13 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2413,10 +2629,13 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2441,10 +2660,13 @@
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2469,10 +2691,13 @@
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2497,10 +2722,13 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2525,10 +2753,13 @@
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2553,10 +2784,13 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2581,10 +2815,13 @@
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2609,10 +2846,13 @@
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2637,10 +2877,13 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2665,10 +2908,13 @@
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2693,10 +2939,13 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2721,10 +2970,13 @@
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2749,10 +3001,13 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2777,10 +3032,13 @@
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2805,10 +3063,13 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2833,10 +3094,13 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2861,10 +3125,13 @@
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2889,10 +3156,13 @@
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2917,10 +3187,13 @@
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2945,10 +3218,13 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2973,10 +3249,13 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3001,10 +3280,13 @@
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3029,10 +3311,13 @@
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3057,10 +3342,13 @@
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3085,10 +3373,13 @@
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3113,10 +3404,13 @@
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3141,10 +3435,13 @@
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3169,10 +3466,13 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3197,10 +3497,13 @@
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3225,10 +3528,13 @@
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3253,10 +3559,13 @@
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3281,10 +3590,13 @@
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3309,10 +3621,13 @@
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3337,10 +3652,13 @@
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3365,10 +3683,13 @@
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3393,10 +3714,13 @@
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3421,10 +3745,13 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3449,10 +3776,13 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3477,10 +3807,13 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3505,10 +3838,13 @@
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3533,10 +3869,13 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3561,10 +3900,13 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3589,10 +3931,13 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3617,10 +3962,13 @@
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3645,10 +3993,13 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3673,10 +4024,13 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3701,10 +4055,13 @@
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3729,10 +4086,13 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3757,10 +4117,13 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3785,10 +4148,13 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3813,10 +4179,13 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3841,10 +4210,13 @@
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3869,10 +4241,13 @@
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3897,10 +4272,13 @@
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3925,10 +4303,13 @@
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3953,10 +4334,13 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3981,10 +4365,13 @@
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4009,10 +4396,13 @@
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4037,10 +4427,13 @@
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4065,10 +4458,13 @@
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4093,10 +4489,13 @@
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4121,10 +4520,13 @@
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4149,10 +4551,13 @@
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4177,10 +4582,13 @@
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4205,10 +4613,13 @@
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4233,10 +4644,13 @@
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4261,10 +4675,13 @@
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4289,10 +4706,13 @@
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4317,10 +4737,13 @@
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4345,10 +4768,13 @@
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4373,10 +4799,13 @@
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4401,10 +4830,13 @@
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4429,10 +4861,13 @@
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4457,10 +4892,13 @@
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4485,10 +4923,13 @@
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4513,10 +4954,13 @@
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4541,10 +4985,13 @@
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4569,13 +5016,16 @@
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J145"/>
+  <autoFilter ref="A1:M145"/>
   <dataValidations count="2">
     <dataValidation sqref="C2:C145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
       <formula1>'Clubs'!$A$2:$A$17</formula1>
@@ -4812,7 +5262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4906,48 +5356,84 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>home_score</t>
+          <t>line_source</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Home points scored. Leave blank until played.</t>
+          <t>Leave blank for a handicap you read off a spread market. "inferred-1x2" means it was derived from win odds by spread_from_odds.py and is an estimate, not a quote.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>away_score</t>
+          <t>home_score</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Away points scored.</t>
+          <t>Home points scored. Leave blank until played.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>home_turnovers_conceded</t>
+          <t>away_score</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Turnovers the HOME side conceded, from the URC match centre. Leave blank until played.</t>
+          <t>Away points scored.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>home_turnovers_conceded</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Turnovers the HOME side conceded, from the URC match centre. Leave blank until played.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>away_turnovers_conceded</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Turnovers the AWAY side conceded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>home_turnovers_won</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Turnovers the HOME side won. Needed as well as conceded: a club's margin is its own conceded minus its own won, and in rugby those are separate counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>away_turnovers_won</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Turnovers the AWAY side won.</t>
         </is>
       </c>
     </row>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to fill this in" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixtures'!$A$1:$N$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -451,14 +451,15 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,40 +490,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>opening_line</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>closing_line</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>line_source</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>home_score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>away_score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>home_turnovers_conceded</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>away_turnovers_conceded</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>home_turnovers_won</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>away_turnovers_won</t>
         </is>
@@ -555,13 +561,18 @@
           <t>-9.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,13 +601,18 @@
           <t>-1.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,13 +641,18 @@
           <t>-11.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-11.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,13 +681,18 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -695,13 +721,18 @@
           <t>-2.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -730,13 +761,18 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -765,13 +801,18 @@
           <t>-12.5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-11.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,13 +841,18 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -831,13 +877,14 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -862,13 +909,14 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -893,13 +941,14 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -924,13 +973,14 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -955,13 +1005,14 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -986,13 +1037,14 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,13 +1069,14 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1048,13 +1101,14 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1079,13 +1133,14 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1110,13 +1165,14 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1141,13 +1197,14 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1172,13 +1229,14 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1203,13 +1261,14 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1234,13 +1293,14 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1265,13 +1325,14 @@
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1296,13 +1357,14 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1327,13 +1389,14 @@
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1358,13 +1421,14 @@
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1389,13 +1453,14 @@
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1420,13 +1485,14 @@
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1451,13 +1517,14 @@
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1482,13 +1549,14 @@
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1513,13 +1581,14 @@
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1544,13 +1613,14 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1575,13 +1645,14 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1606,13 +1677,14 @@
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1637,13 +1709,14 @@
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1668,13 +1741,14 @@
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1699,13 +1773,14 @@
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1730,13 +1805,14 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1761,13 +1837,14 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1792,13 +1869,14 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1823,13 +1901,14 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1854,13 +1933,14 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1885,13 +1965,14 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1916,13 +1997,14 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1947,13 +2029,14 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1978,13 +2061,14 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2009,13 +2093,14 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2040,13 +2125,14 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2071,13 +2157,14 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2102,13 +2189,14 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2133,13 +2221,14 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2164,13 +2253,14 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2195,13 +2285,14 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2226,13 +2317,14 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2257,13 +2349,14 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2288,13 +2381,14 @@
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2319,13 +2413,14 @@
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2350,13 +2445,14 @@
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2381,13 +2477,14 @@
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2412,13 +2509,14 @@
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2443,13 +2541,14 @@
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2474,13 +2573,14 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2505,13 +2605,14 @@
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2536,13 +2637,14 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2567,13 +2669,14 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,13 +2701,14 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2629,13 +2733,14 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2660,13 +2765,14 @@
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2691,13 +2797,14 @@
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2722,13 +2829,14 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2753,13 +2861,14 @@
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2784,13 +2893,14 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2815,13 +2925,14 @@
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2846,13 +2957,14 @@
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2877,13 +2989,14 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2908,13 +3021,14 @@
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2939,13 +3053,14 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2970,13 +3085,14 @@
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3001,13 +3117,14 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3032,13 +3149,14 @@
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3063,13 +3181,14 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3094,13 +3213,14 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3125,13 +3245,14 @@
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3156,13 +3277,14 @@
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3187,13 +3309,14 @@
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3218,13 +3341,14 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3249,13 +3373,14 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3280,13 +3405,14 @@
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3311,13 +3437,14 @@
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3342,13 +3469,14 @@
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3373,13 +3501,14 @@
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3404,13 +3533,14 @@
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3435,13 +3565,14 @@
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3466,13 +3597,14 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3497,13 +3629,14 @@
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3528,13 +3661,14 @@
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,13 +3693,14 @@
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3590,13 +3725,14 @@
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3621,13 +3757,14 @@
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3652,13 +3789,14 @@
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3683,13 +3821,14 @@
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3714,13 +3853,14 @@
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3745,13 +3885,14 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3776,13 +3917,14 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3807,13 +3949,14 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3838,13 +3981,14 @@
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3869,13 +4013,14 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3900,13 +4045,14 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3931,13 +4077,14 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3962,13 +4109,14 @@
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3993,13 +4141,14 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4024,13 +4173,14 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4055,13 +4205,14 @@
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4086,13 +4237,14 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4117,13 +4269,14 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
       <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4148,13 +4301,14 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4179,13 +4333,14 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4210,13 +4365,14 @@
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
       <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4241,13 +4397,14 @@
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
       <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4272,13 +4429,14 @@
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
       <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4303,13 +4461,14 @@
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
       <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4334,13 +4493,14 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4365,13 +4525,14 @@
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4396,13 +4557,14 @@
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4427,13 +4589,14 @@
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4458,13 +4621,14 @@
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
       <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4489,13 +4653,14 @@
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
       <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4520,13 +4685,14 @@
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4551,13 +4717,14 @@
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4582,13 +4749,14 @@
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
       <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4613,13 +4781,14 @@
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
       <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4644,13 +4813,14 @@
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
       <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4675,13 +4845,14 @@
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
       <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4706,13 +4877,14 @@
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
       <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4737,13 +4909,14 @@
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
       <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4768,13 +4941,14 @@
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
       <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4799,13 +4973,14 @@
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
       <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4830,13 +5005,14 @@
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
       <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4861,13 +5037,14 @@
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4892,13 +5069,14 @@
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
       <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4923,13 +5101,14 @@
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4954,13 +5133,14 @@
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
       <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4985,13 +5165,14 @@
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5016,16 +5197,17 @@
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M145"/>
+  <autoFilter ref="A1:N145"/>
   <dataValidations count="2">
     <dataValidation sqref="C2:C145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a URC club" error="Pick a club from the Clubs sheet." type="list">
       <formula1>'Clubs'!$A$2:$A$17</formula1>
@@ -5262,7 +5444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5344,94 +5526,106 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>opening_line</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>THE HANDICAP, from the home team's point of view. NEGATIVE = home favoured (-7.5 means home must win by 8 to cover); POSITIVE = home receiving points. This is the one number needed to make a pick.</t>
+          <t>The handicap when the round is first priced, from the home team's point of view. NEGATIVE = home favoured (-7.5 means home must win by 8 to cover); POSITIVE = home receiving points. The model picks on it only until closing_line is filled; after that it is kept as a record of the move.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>line_source</t>
+          <t>closing_line</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Leave blank for a handicap you read off a spread market. "inferred-1x2" means it was derived from win odds by spread_from_odds.py and is an estimate, not a quote.</t>
+          <t>The handicap as late as practical before kick-off - after the teams are named. Same sign convention. THIS is the line the model picks, rates and grades on, as nfl_report does. Leave blank until you have it.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>home_score</t>
+          <t>line_source</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Home points scored. Leave blank until played.</t>
+          <t>Leave blank for a handicap you read off a spread market. "inferred-1x2" means it was derived from win odds by spread_from_odds.py and is an estimate, not a quote.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>away_score</t>
+          <t>home_score</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Away points scored.</t>
+          <t>Home points scored. Leave blank until played.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>home_turnovers_conceded</t>
+          <t>away_score</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Turnovers the HOME side conceded, from the URC match centre. Leave blank until played.</t>
+          <t>Away points scored.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>away_turnovers_conceded</t>
+          <t>home_turnovers_conceded</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Turnovers the AWAY side conceded.</t>
+          <t>Turnovers the HOME side conceded, from the URC match centre. Leave blank until played.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>home_turnovers_won</t>
+          <t>away_turnovers_conceded</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Turnovers the HOME side won. Needed as well as conceded: a club's margin is its own conceded minus its own won, and in rugby those are separate counts.</t>
+          <t>Turnovers the AWAY side conceded.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>home_turnovers_won</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Turnovers the HOME side won. Needed as well as conceded: a club's margin is its own conceded minus its own won, and in rugby those are separate counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>away_turnovers_won</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Turnovers the AWAY side won.</t>
         </is>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -567,12 +567,36 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -607,12 +631,36 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -647,12 +695,36 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,7 +755,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -723,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -803,7 +875,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -759,12 +759,36 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -799,12 +823,36 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -839,12 +887,36 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -879,12 +951,36 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -919,12 +1015,36 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -948,7 +1068,11 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
@@ -980,7 +1104,11 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-17.5</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1012,7 +1140,11 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1044,7 +1176,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1076,7 +1212,11 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-13.5</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1108,7 +1248,11 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1140,7 +1284,11 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1172,7 +1320,11 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -5687,7 +5839,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Turnovers the HOME side won. Needed as well as conceded: a club's margin is its own conceded minus its own won, and in rugby those are separate counts.</t>
+          <t>Turnovers the HOME side won. Recorded for analysis; the model reads turnovers conceded only (home minus away), so a blank here blocks nothing.</t>
         </is>
       </c>
     </row>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1073,7 +1073,11 @@
           <t>-4.5</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1109,7 +1113,11 @@
           <t>-17.5</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1145,7 +1153,11 @@
           <t>-5.5</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1181,7 +1193,11 @@
           <t>-2.5</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1217,7 +1233,11 @@
           <t>-13.5</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-13.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1253,7 +1273,11 @@
           <t>-10.5</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1289,7 +1313,11 @@
           <t>-5.5</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1325,7 +1353,11 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18.5</t>
+          <t>-20.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-14.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1079,12 +1079,36 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1119,12 +1143,36 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1159,12 +1207,36 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1199,12 +1271,36 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1239,12 +1335,36 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1279,12 +1399,36 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1319,12 +1463,36 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1359,12 +1527,36 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1388,7 +1580,11 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1420,7 +1616,11 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1452,7 +1652,11 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1484,7 +1688,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-21.5</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1516,7 +1724,11 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1548,7 +1760,11 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1580,7 +1796,11 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1612,7 +1832,11 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1585,7 +1585,11 @@
           <t>-2.5</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1621,7 +1625,11 @@
           <t>-12.5</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1657,7 +1665,11 @@
           <t>-8.5</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1693,7 +1705,11 @@
           <t>-21.5</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1729,7 +1745,11 @@
           <t>-4.5</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1765,7 +1785,11 @@
           <t>-7.5</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1801,7 +1825,11 @@
           <t>-4.5</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1837,7 +1865,11 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -1591,12 +1591,36 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1631,12 +1655,36 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1671,12 +1719,36 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1711,12 +1783,36 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1751,12 +1847,36 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1791,12 +1911,36 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1831,12 +1975,36 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1871,12 +2039,36 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2092,7 +2092,11 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2124,7 +2128,11 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2156,7 +2164,11 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2188,7 +2200,11 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2220,7 +2236,11 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2252,7 +2272,11 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-15.5</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2284,7 +2308,11 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2316,7 +2344,11 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>-21.5</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2097,7 +2097,11 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
@@ -2133,7 +2137,11 @@
           <t>-18.5</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-21.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
@@ -2169,7 +2177,11 @@
           <t>-8.5</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
@@ -2205,7 +2217,11 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2241,7 +2257,11 @@
           <t>-18.5</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-16.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2277,7 +2297,11 @@
           <t>-15.5</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>-16.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2313,7 +2337,11 @@
           <t>-8.5</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2349,7 +2377,11 @@
           <t>-21.5</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>-22.5</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21.5</t>
+          <t>-22.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-16.5</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2412,7 +2412,11 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2444,7 +2448,11 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2476,7 +2484,11 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2508,7 +2520,11 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-21.0</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2540,7 +2556,11 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2572,7 +2592,11 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2604,7 +2628,11 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2636,7 +2664,11 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2103,12 +2103,36 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2143,12 +2167,36 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2183,12 +2231,36 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2223,12 +2295,36 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2263,12 +2359,36 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2303,12 +2423,36 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2343,12 +2487,36 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2383,12 +2551,36 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2414,7 +2606,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -2450,7 +2642,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-14.5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2486,7 +2678,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -2522,7 +2714,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-21.5</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -2558,7 +2750,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2594,7 +2786,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2630,7 +2822,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -2666,7 +2858,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>

--- a/rugby_urc/entry/urc_2026_entry.xlsx
+++ b/rugby_urc/entry/urc_2026_entry.xlsx
@@ -2609,7 +2609,11 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2645,7 +2649,11 @@
           <t>-14.5</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
@@ -2681,7 +2689,11 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2717,7 +2729,11 @@
           <t>-21.5</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>-25.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
@@ -2753,7 +2769,11 @@
           <t>-10.5</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2789,7 +2809,11 @@
           <t>-6.5</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
@@ -2825,7 +2849,11 @@
           <t>-3.5</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2861,7 +2889,11 @@
           <t>-12.5</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>-16.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
